--- a/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/ModCkGradePdConfig001.xlsx
+++ b/tams-valuation-parent/tams-valuation-lossmodel/src/main/resources/tpl/ModCkGradePdConfig001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projectManager\company\BS_branches_I9\tams-model-impairment\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projectManager\company\zgbs3.0_tams\tams\tams-valuation-parent\tams-valuation-lossmodel\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13590" windowHeight="5990"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13596" windowHeight="5988"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -370,21 +370,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N43"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.90625" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="8" max="11" width="12.453125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.453125" customWidth="1"/>
-    <col min="13" max="13" width="12.90625" customWidth="1"/>
-    <col min="14" max="14" width="12.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="11" width="12.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -568,11 +568,17 @@
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
     </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5 B2:B43">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5">
       <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,13:BBB+,14:BBB,15:BBB-,17:BB,20:B,23:CCC,26:CC,29:C,31:D"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B44">
+      <formula1>"01:AAA+,02:AAA,03:AAA-,04:AA+,05:AA,06:AA-,07:A+,08:A,09:A-,10:BBB+,11:BBB,12:BBB-,13:BB+,14:BB,15:BB-,16:B,17:CCC+,18:CCC,19:CCC-,20:CC+,21:CC,22:CC-,23:C+,24:C,25:C-,26:D"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
